--- a/exports/trend_1d/MANKIND_full_report.xlsx
+++ b/exports/trend_1d/MANKIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>13.09</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45135</v>
+        <v>45138</v>
       </c>
       <c r="H2" t="n">
-        <v>1814.85</v>
+        <v>1742.75</v>
       </c>
       <c r="I2" t="n">
         <v>1749.182537908456</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>36.33</v>
+        <v>30.91</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.61</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H3" t="n">
-        <v>1793.8</v>
+        <v>1843.6</v>
       </c>
       <c r="I3" t="n">
         <v>1840.637537936448</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.93</v>
+        <v>-5.79</v>
       </c>
       <c r="L3" t="n">
         <v>11.61</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.26</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="H4" t="n">
-        <v>2190.75</v>
+        <v>2092.55</v>
       </c>
       <c r="I4" t="n">
         <v>2156.313905454165</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K4" t="n">
-        <v>18.83</v>
+        <v>13.5</v>
       </c>
       <c r="L4" t="n">
         <v>2.52</v>
@@ -669,7 +716,7 @@
         <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4.48</v>
       </c>
       <c r="O4" t="n">
         <v>2.78</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>18.62</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45516</v>
+        <v>45517</v>
       </c>
       <c r="H5" t="n">
-        <v>2152.05</v>
+        <v>2175.65</v>
       </c>
       <c r="I5" t="n">
         <v>2154.714280059707</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.84</v>
+        <v>-3.97</v>
       </c>
       <c r="L5" t="n">
         <v>9.869999999999999</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.99</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="H6" t="n">
-        <v>2455.9</v>
+        <v>2426.8</v>
       </c>
       <c r="I6" t="n">
         <v>2446.019016980458</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K6" t="n">
-        <v>12.88</v>
+        <v>11.54</v>
       </c>
       <c r="L6" t="n">
         <v>2.53</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45597</v>
+        <v>45600</v>
       </c>
       <c r="H7" t="n">
-        <v>2680.7</v>
+        <v>2731.2</v>
       </c>
       <c r="I7" t="n">
         <v>2705.899572637176</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.46</v>
+        <v>-12.54</v>
       </c>
       <c r="L7" t="n">
-        <v>12.58</v>
+        <v>13.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.98</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H8" t="n">
-        <v>2739.95</v>
+        <v>2595.95</v>
       </c>
       <c r="I8" t="n">
         <v>2618.228032761457</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K8" t="n">
-        <v>0.32</v>
+        <v>-4.95</v>
       </c>
       <c r="L8" t="n">
         <v>8.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>3.17</v>
       </c>
       <c r="N8" t="n">
-        <v>3.43</v>
+        <v>5.26</v>
       </c>
       <c r="O8" t="n">
         <v>1.88</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H9" t="n">
-        <v>2244.85</v>
+        <v>2415.05</v>
       </c>
       <c r="I9" t="n">
         <v>2395.696935262674</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K9" t="n">
-        <v>13.52</v>
+        <v>6.97</v>
       </c>
       <c r="L9" t="n">
         <v>6.12</v>
@@ -954,7 +1061,7 @@
         <v>1.92</v>
       </c>
       <c r="N9" t="n">
-        <v>4.72</v>
+        <v>7.58</v>
       </c>
       <c r="O9" t="n">
         <v>-5.26</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>14.4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H10" t="n">
-        <v>2358.3</v>
+        <v>2325.2</v>
       </c>
       <c r="I10" t="n">
         <v>2338.338210021565</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.35</v>
+        <v>-3.72</v>
       </c>
       <c r="L10" t="n">
         <v>6.71</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.99</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="H11" t="n">
-        <v>2431.7</v>
+        <v>2526.6</v>
       </c>
       <c r="I11" t="n">
         <v>2440.477772319427</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.58</v>
+        <v>-8.66</v>
       </c>
       <c r="L11" t="n">
-        <v>6.04</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>0.86</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45877</v>
+        <v>45880</v>
       </c>
       <c r="H12" t="n">
-        <v>2467.1</v>
+        <v>2437.5</v>
       </c>
       <c r="I12" t="n">
         <v>2456.370092391271</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.35</v>
+        <v>-3.53</v>
       </c>
       <c r="L12" t="n">
         <v>4.31</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.67</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="H13" t="n">
-        <v>2638.3</v>
+        <v>2660.6</v>
       </c>
       <c r="I13" t="n">
         <v>2653.65199606204</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.24</v>
+        <v>-9.15</v>
       </c>
       <c r="L13" t="n">
-        <v>9.119999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>1.99</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>6.5</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H14" t="n">
-        <v>2526.2</v>
+        <v>2482.9</v>
       </c>
       <c r="I14" t="n">
         <v>2487.704184850917</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.05</v>
+        <v>-6.68</v>
       </c>
       <c r="L14" t="n">
-        <v>5.66</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.38</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
         <v>2.47</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.7</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="H15" t="n">
-        <v>2186.3</v>
+        <v>2229.6</v>
       </c>
       <c r="I15" t="n">
         <v>2226.188556326642</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="n">
-        <v>11.95</v>
+        <v>10.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.25</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.28</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H16" t="n">
-        <v>2175.4</v>
+        <v>2117.2</v>
       </c>
       <c r="I16" t="n">
         <v>2131.333937818239</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.43</v>
+        <v>-5.04</v>
       </c>
       <c r="L16" t="n">
-        <v>3.74</v>
+        <v>5.35</v>
       </c>
       <c r="M16" t="n">
         <v>0.78</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.07</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="H17" t="n">
-        <v>2155.7</v>
+        <v>2279.7</v>
       </c>
       <c r="I17" t="n">
         <v>2167.356995288697</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.82</v>
+        <v>-7.68</v>
       </c>
       <c r="L17" t="n">
-        <v>3.86</v>
+        <v>7.92</v>
       </c>
       <c r="M17" t="n">
         <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.92</v>
+        <v>5.75</v>
       </c>
       <c r="O17" t="n">
         <v>-2.68</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>10.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="H18" t="n">
-        <v>2094.7</v>
+        <v>2068.2</v>
       </c>
       <c r="I18" t="n">
         <v>2080.606550391086</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.119999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>8.720000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="M18" t="n">
         <v>3.85</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.44</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H19" t="n">
-        <v>2144</v>
+        <v>2200</v>
       </c>
       <c r="I19" t="n">
         <v>2159.090892992983</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.67</v>
+        <v>-6.37</v>
       </c>
       <c r="L19" t="n">
-        <v>4.82</v>
+        <v>6.67</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.48</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H20" t="n">
-        <v>2375.6</v>
+        <v>2320.2</v>
       </c>
       <c r="I20" t="n">
         <v>2324.563613522856</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>7.98</v>
+        <v>5.46</v>
       </c>
       <c r="L20" t="n">
         <v>2.86</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>12.38</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="H21" t="n">
-        <v>2414.2</v>
+        <v>2538.3</v>
       </c>
       <c r="I21" t="n">
         <v>2532.444592017298</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.05</v>
+        <v>-9.4</v>
       </c>
       <c r="L21" t="n">
-        <v>4.73</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>1.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3.07</v>
+        <v>5.14</v>
       </c>
       <c r="O21" t="n">
         <v>-2.33</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.25</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="H22" t="n">
-        <v>2433.1</v>
+        <v>2404.4</v>
       </c>
       <c r="I22" t="n">
         <v>2414.785149066574</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.14</v>
+        <v>-5.28</v>
       </c>
       <c r="L22" t="n">
         <v>6.19</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.36</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="H23" t="n">
-        <v>2300.7</v>
+        <v>2437.8</v>
       </c>
       <c r="I23" t="n">
         <v>2401.692498840998</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K23" t="n">
-        <v>4.31</v>
+        <v>-1.39</v>
       </c>
       <c r="L23" t="n">
         <v>2.23</v>
@@ -1752,7 +2027,7 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>5.96</v>
       </c>
       <c r="O23" t="n">
         <v>-1.18</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>10</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H24" t="n">
-        <v>2347.6</v>
+        <v>2275.5</v>
       </c>
       <c r="I24" t="n">
         <v>2314.613265386917</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.7</v>
+        <v>-6.66</v>
       </c>
       <c r="L24" t="n">
-        <v>5.53</v>
+        <v>6.94</v>
       </c>
       <c r="M24" t="n">
         <v>0.91</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.27</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H25" t="n">
-        <v>2312</v>
+        <v>2502.5</v>
       </c>
       <c r="I25" t="n">
         <v>2451.144057195024</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6</v>
+        <v>-9.98</v>
       </c>
       <c r="L25" t="n">
-        <v>3.47</v>
+        <v>11.18</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5</v>
+        <v>2.01</v>
       </c>
       <c r="N25" t="n">
-        <v>4.49</v>
+        <v>8.24</v>
       </c>
       <c r="O25" t="n">
         <v>-3.07</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1926,6 +2237,12 @@
       <c r="Q26" t="n">
         <v>2</v>
       </c>
+      <c r="R26" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3484,7 +3801,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="6">
@@ -3494,7 +3811,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -3504,7 +3821,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
@@ -3514,7 +3831,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3524,7 +3841,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="10">
@@ -3534,7 +3851,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88.7</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="11">
@@ -3544,7 +3861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -3554,7 +3871,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -3564,7 +3881,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="14">
@@ -3574,7 +3891,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.57</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="15">
@@ -3584,7 +3901,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.02</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16">
@@ -3594,7 +3911,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.87</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="17">
@@ -3604,7 +3921,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36.33</v>
+        <v>30.91</v>
       </c>
     </row>
     <row r="18">
@@ -3614,7 +3931,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -3624,7 +3941,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.58</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="20">
@@ -3634,7 +3951,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.18</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="21">
@@ -3644,7 +3961,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.58</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="22">
@@ -3654,7 +3971,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -3664,7 +3981,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -3674,7 +3991,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="25">
@@ -3694,7 +4011,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.87</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="27">
@@ -3714,7 +4031,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
